--- a/test/fixtures/xlsx/text/text.xlsx
+++ b/test/fixtures/xlsx/text/text.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="55">
   <si>
     <t xml:space="preserve">~~table:Quest~~</t>
   </si>
@@ -65,7 +65,7 @@
     <t xml:space="preserve">Hint</t>
   </si>
   <si>
-    <t xml:space="preserve">may be blank</t>
+    <t xml:space="preserve">`-` or blank</t>
   </si>
   <si>
     <t xml:space="preserve">text?</t>
@@ -102,6 +102,9 @@
   </si>
   <si>
     <t xml:space="preserve">quest_lost_cargo_2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-</t>
   </si>
   <si>
     <t xml:space="preserve">Hello;Farewell</t>
@@ -365,60 +368,60 @@
         <v>29</v>
       </c>
       <c r="F10" t="s">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="G10" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="11">
       <c r="B11" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C11" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D11" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E11" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F11" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G11" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="12">
       <c r="B12" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C12" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D12" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E12" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F12" t="s">
         <v>5</v>
       </c>
       <c r="G12" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="15">
       <c r="B15" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="16">
       <c r="B16" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="17">
@@ -426,13 +429,13 @@
         <v>2</v>
       </c>
       <c r="C17" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D17" t="s">
         <v>10</v>
       </c>
       <c r="E17" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="18">
@@ -440,13 +443,13 @@
         <v>3</v>
       </c>
       <c r="C18" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D18" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E18" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="19">
@@ -474,7 +477,7 @@
         <v>5</v>
       </c>
       <c r="E20" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="21">
@@ -496,13 +499,13 @@
         <v>22</v>
       </c>
       <c r="C22" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D22" t="s">
         <v>24</v>
       </c>
       <c r="E22" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="23">
@@ -510,13 +513,13 @@
         <v>28</v>
       </c>
       <c r="C23" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D23" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E23" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
   </sheetData>
